--- a/output/pdf_financials_xlsx/FTN.xlsx
+++ b/output/pdf_financials_xlsx/FTN.xlsx
@@ -2081,34 +2081,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>18.110076</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>15.795954</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>20.828563</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>4.303322</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>16.91764</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>78.46978</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>40.515641</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>66.10696299999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>28.116331</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>129.119624</v>
       </c>
     </row>
     <row r="35">
@@ -2165,34 +2165,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>18.110076</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>15.795954</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>20.828563</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>4.303322</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>16.91764</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>78.46978</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>40.515641</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>66.10696299999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>28.116331</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>129.119624</v>
       </c>
     </row>
     <row r="37">
@@ -2672,31 +2672,31 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>191.832083</v>
+        <v>176.036129</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>263.943655</v>
+        <v>243.115092</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>281.44066</v>
+        <v>277.137338</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>331.430799</v>
+        <v>314.513159</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>632.040562</v>
+        <v>553.570782</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>650.754824</v>
+        <v>610.239183</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>704.698116</v>
+        <v>638.591153</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>508.249756</v>
+        <v>480.133425</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>669.637064</v>
+        <v>540.51744</v>
       </c>
     </row>
     <row r="49">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
